--- a/data/trans_orig/P33B4_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B4_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que se siente cansado cuando despierta por la mañana en 2023</t>
+          <t>Población según la frecuencia con la que se siente cansado cuando despierta por la mañana en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60227</t>
+          <t>59738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88756</t>
+          <t>90186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141473</t>
+          <t>141910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174151</t>
+          <t>173804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>207713</t>
+          <t>208256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251690</t>
+          <t>252193</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40711</t>
+          <t>41083</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63565</t>
+          <t>64058</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93570</t>
+          <t>92460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127565</t>
+          <t>127445</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141013</t>
+          <t>140751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181798</t>
+          <t>180355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55022</t>
+          <t>56632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84683</t>
+          <t>85895</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>151665</t>
+          <t>150288</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>185449</t>
+          <t>182580</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>215388</t>
+          <t>214226</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>260160</t>
+          <t>259834</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>300458</t>
+          <t>302056</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>341153</t>
+          <t>341042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>301134</t>
+          <t>299343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>342330</t>
+          <t>340997</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>609527</t>
+          <t>612367</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>671836</t>
+          <t>673340</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86423</t>
+          <t>85239</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>152015</t>
+          <t>152254</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>134212</t>
+          <t>138214</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>216886</t>
+          <t>217576</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>243919</t>
+          <t>246311</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>354020</t>
+          <t>352779</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82344</t>
+          <t>85477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150216</t>
+          <t>150169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136942</t>
+          <t>139732</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>222311</t>
+          <t>221784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>252855</t>
+          <t>251313</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>357523</t>
+          <t>353741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228326</t>
+          <t>221046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>377399</t>
+          <t>379797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>302745</t>
+          <t>296074</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>467380</t>
+          <t>467827</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>579244</t>
+          <t>593743</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>817667</t>
+          <t>819721</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1634247</t>
+          <t>1634950</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1900204</t>
+          <t>1903988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1350165</t>
+          <t>1350048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1658897</t>
+          <t>1659541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3028787</t>
+          <t>3035028</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3448903</t>
+          <t>3423530</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,64%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22517</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50338</t>
+          <t>49221</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40527</t>
+          <t>42117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67683</t>
+          <t>67515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69624</t>
+          <t>70310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>107488</t>
+          <t>108891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28777</t>
+          <t>27510</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56833</t>
+          <t>53079</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48898</t>
+          <t>48164</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75691</t>
+          <t>73361</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>82144</t>
+          <t>83402</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119271</t>
+          <t>121083</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119429</t>
+          <t>119392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170139</t>
+          <t>171506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122541</t>
+          <t>124004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157699</t>
+          <t>159484</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>258271</t>
+          <t>257462</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320616</t>
+          <t>316678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>403026</t>
+          <t>396576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455849</t>
+          <t>457483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>384546</t>
+          <t>385973</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>426262</t>
+          <t>429369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>801072</t>
+          <t>797350</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>867816</t>
+          <t>869284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,55%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>175762</t>
+          <t>179575</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>267655</t>
+          <t>266772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>324483</t>
+          <t>324846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>437401</t>
+          <t>439182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>545570</t>
+          <t>539821</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>689105</t>
+          <t>682405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166597</t>
+          <t>168811</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249551</t>
+          <t>246419</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>288358</t>
+          <t>292612</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>398050</t>
+          <t>401247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>500668</t>
+          <t>488126</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>624926</t>
+          <t>626788</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>419449</t>
+          <t>416150</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>595320</t>
+          <t>597676</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>579413</t>
+          <t>594288</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>786773</t>
+          <t>779244</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1091711</t>
+          <t>1089359</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1339325</t>
+          <t>1353748</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2371203</t>
+          <t>2374967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2699707</t>
+          <t>2685524</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2057653</t>
+          <t>2057521</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2492847</t>
+          <t>2434900</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4491343</t>
+          <t>4475086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4978591</t>
+          <t>4978180</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B4_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33B4_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>72688</t>
+          <t>78695</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59738</t>
+          <t>64669</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90186</t>
+          <t>96836</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>156523</t>
+          <t>175612</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141910</t>
+          <t>157333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173804</t>
+          <t>194140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>229212</t>
+          <t>254307</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208256</t>
+          <t>231317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>252193</t>
+          <t>279015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51334</t>
+          <t>54323</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41083</t>
+          <t>43202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64058</t>
+          <t>68210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>107527</t>
+          <t>115150</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92460</t>
+          <t>99025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127445</t>
+          <t>129916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>158861</t>
+          <t>169473</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>140751</t>
+          <t>151021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>180355</t>
+          <t>189870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69197</t>
+          <t>77500</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56632</t>
+          <t>63996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85895</t>
+          <t>93154</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>167294</t>
+          <t>180207</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>150288</t>
+          <t>164542</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>182580</t>
+          <t>197859</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236491</t>
+          <t>257706</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>214226</t>
+          <t>234854</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>259834</t>
+          <t>280941</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>321718</t>
+          <t>368011</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>302056</t>
+          <t>344580</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>341042</t>
+          <t>388484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>320771</t>
+          <t>349192</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>299343</t>
+          <t>326471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>340997</t>
+          <t>372962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>642489</t>
+          <t>717203</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>612367</t>
+          <t>687661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>673340</t>
+          <t>747006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>752115</t>
+          <t>820160</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>752115</t>
+          <t>820160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>752115</t>
+          <t>820160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1267053</t>
+          <t>1398689</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1267053</t>
+          <t>1398689</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1267053</t>
+          <t>1398689</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>123479</t>
+          <t>138442</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85239</t>
+          <t>114936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>152254</t>
+          <t>164897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>184973</t>
+          <t>211804</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138214</t>
+          <t>187828</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>217576</t>
+          <t>242116</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>308452</t>
+          <t>350246</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>246311</t>
+          <t>315098</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>352779</t>
+          <t>385822</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>122061</t>
+          <t>130810</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85477</t>
+          <t>110979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150169</t>
+          <t>160174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>188962</t>
+          <t>210424</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>139732</t>
+          <t>186964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>221784</t>
+          <t>235781</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>311023</t>
+          <t>341234</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>251313</t>
+          <t>306524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>353741</t>
+          <t>378217</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>322162</t>
+          <t>360598</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>221046</t>
+          <t>323733</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>379797</t>
+          <t>398543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>407754</t>
+          <t>452488</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296074</t>
+          <t>421808</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>467827</t>
+          <t>487548</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>729916</t>
+          <t>813086</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>593743</t>
+          <t>766739</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>819721</t>
+          <t>866250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1720580</t>
+          <t>1598656</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1634950</t>
+          <t>1554136</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1903988</t>
+          <t>1648412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1456134</t>
+          <t>1296676</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1350048</t>
+          <t>1252584</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1659541</t>
+          <t>1335699</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3176714</t>
+          <t>2895332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3035028</t>
+          <t>2828228</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3423530</t>
+          <t>2957723</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>67,22%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2288281</t>
+          <t>2228506</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2288281</t>
+          <t>2228506</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2288281</t>
+          <t>2228506</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4526105</t>
+          <t>4399898</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4526105</t>
+          <t>4399898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4526105</t>
+          <t>4399898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>37987</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>26099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49221</t>
+          <t>58264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>52995</t>
+          <t>58037</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42117</t>
+          <t>44164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>72306</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>86812</t>
+          <t>96024</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70310</t>
+          <t>78311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108891</t>
+          <t>119382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39267</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27510</t>
+          <t>34333</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53079</t>
+          <t>63317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>60199</t>
+          <t>67779</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48164</t>
+          <t>55142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73361</t>
+          <t>83247</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>99466</t>
+          <t>114514</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>83402</t>
+          <t>94882</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>121083</t>
+          <t>136692</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>142966</t>
+          <t>148566</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119392</t>
+          <t>126541</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171506</t>
+          <t>172052</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>140331</t>
+          <t>157667</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124004</t>
+          <t>139782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159484</t>
+          <t>179255</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>283297</t>
+          <t>306233</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257462</t>
+          <t>279029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>316678</t>
+          <t>339269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -2202,67 +2202,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>429604</t>
+          <t>477312</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>396576</t>
+          <t>449026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>457483</t>
+          <t>503167</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>63,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>451394</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>427133</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>474666</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>61,42%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>406938</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>385973</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>429369</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>61,61%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>836542</t>
+          <t>928706</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>797350</t>
+          <t>892867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>869284</t>
+          <t>964951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,76%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>645654</t>
+          <t>710599</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1306117</t>
+          <t>1445477</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>229984</t>
+          <t>255124</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>179575</t>
+          <t>224168</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>266772</t>
+          <t>289864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>394491</t>
+          <t>445453</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>324846</t>
+          <t>413545</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>439182</t>
+          <t>477474</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>624475</t>
+          <t>700577</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>539821</t>
+          <t>656066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>682405</t>
+          <t>746487</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>212662</t>
+          <t>231868</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168811</t>
+          <t>203362</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>246419</t>
+          <t>265468</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>356688</t>
+          <t>393353</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>292612</t>
+          <t>365018</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>401247</t>
+          <t>433687</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>569350</t>
+          <t>625220</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488126</t>
+          <t>584894</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>626788</t>
+          <t>672452</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>534324</t>
+          <t>586664</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>416150</t>
+          <t>540204</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>597676</t>
+          <t>632695</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>715379</t>
+          <t>790361</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>594288</t>
+          <t>748167</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>779244</t>
+          <t>832429</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1249704</t>
+          <t>1377026</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1089359</t>
+          <t>1316967</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1353748</t>
+          <t>1444006</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2471903</t>
+          <t>2443979</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2374967</t>
+          <t>2386309</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2685524</t>
+          <t>2500457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2183843</t>
+          <t>2097262</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2057521</t>
+          <t>2044262</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2434900</t>
+          <t>2149073</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4655746</t>
+          <t>4541241</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4475086</t>
+          <t>4465123</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4978180</t>
+          <t>4619866</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>63,77%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3448874</t>
+          <t>3517635</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3448874</t>
+          <t>3517635</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3448874</t>
+          <t>3517635</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3650401</t>
+          <t>3726429</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3650401</t>
+          <t>3726429</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3650401</t>
+          <t>3726429</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7099275</t>
+          <t>7244064</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7099275</t>
+          <t>7244064</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7099275</t>
+          <t>7244064</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
